--- a/artfynd/A 26221-2026 artfynd.xlsx
+++ b/artfynd/A 26221-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89915643</v>
+        <v>122530059</v>
       </c>
       <c r="B2" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100067</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,21 +710,25 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällmark, N telemasten, Porshanken, Upl</t>
+          <t>Porshanken, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>708568.1227144042</v>
+        <v>708554</v>
       </c>
       <c r="R2" t="n">
-        <v>6633376.403579527</v>
+        <v>6633149</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,27 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-01-02</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-01-02</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lyfte från träd.</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,51 +794,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89915745</v>
+        <v>89915643</v>
       </c>
       <c r="B3" t="n">
-        <v>56521</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103035</v>
+        <v>100067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -852,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>708568.1227144042</v>
+        <v>708568</v>
       </c>
       <c r="R3" t="n">
-        <v>6633376.403579527</v>
+        <v>6633376</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -900,6 +885,11 @@
           <t>11:45</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lyfte från träd.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -921,125 +911,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>122530059</v>
-      </c>
-      <c r="B4" t="n">
-        <v>57825</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100001</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Duvhök</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Astur gentilis</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Porshanken, Upl</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>708554</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6633149</v>
-      </c>
-      <c r="S4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Norrtälje</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Estuna</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-02-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2025-02-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Magnus Bladlund</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Magnus Bladlund</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26221-2026 artfynd.xlsx
+++ b/artfynd/A 26221-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122530059</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,8 +921,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89915643</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>